--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260813.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260813.xlsx
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>國產</t>
+          <t>正新</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>117,699,000</t>
+          <t>119,300,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>正新</t>
+          <t>國產</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>119,300,000</t>
+          <t>117,699,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>義隆</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>15,470,000</t>
+          <t>27,850,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>義隆</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>27,850,000</t>
+          <t>15,470,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
